--- a/reports/Debug-snowbowl-20260105/For The Day (Actual)_Payroll.xlsx
+++ b/reports/Debug-snowbowl-20260105/For The Day (Actual)_Payroll.xlsx
@@ -14,14 +14,59 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="259">
   <si>
     <t>eecode</t>
   </si>
   <si>
+    <t>A337</t>
+  </si>
+  <si>
+    <t>A0BA</t>
+  </si>
+  <si>
+    <t>G697</t>
+  </si>
+  <si>
+    <t>A2DQ</t>
+  </si>
+  <si>
+    <t>A2C6</t>
+  </si>
+  <si>
+    <t>G961</t>
+  </si>
+  <si>
+    <t>E483</t>
+  </si>
+  <si>
+    <t>D954</t>
+  </si>
+  <si>
+    <t>B884</t>
+  </si>
+  <si>
+    <t>I304</t>
+  </si>
+  <si>
     <t>A749</t>
   </si>
   <si>
+    <t>A2BR</t>
+  </si>
+  <si>
+    <t>A2C5</t>
+  </si>
+  <si>
+    <t>A0AF</t>
+  </si>
+  <si>
+    <t>A31F</t>
+  </si>
+  <si>
+    <t>A3MT</t>
+  </si>
+  <si>
     <t>F058</t>
   </si>
   <si>
@@ -31,190 +76,184 @@
     <t>A3MW</t>
   </si>
   <si>
+    <t>H632</t>
+  </si>
+  <si>
+    <t>A3MD</t>
+  </si>
+  <si>
+    <t>A1K3</t>
+  </si>
+  <si>
+    <t>A2DS</t>
+  </si>
+  <si>
+    <t>A3MR</t>
+  </si>
+  <si>
+    <t>A0BB</t>
+  </si>
+  <si>
+    <t>C346</t>
+  </si>
+  <si>
+    <t>A3OL</t>
+  </si>
+  <si>
+    <t>A3NO</t>
+  </si>
+  <si>
     <t>D521</t>
   </si>
   <si>
-    <t>A0BA</t>
-  </si>
-  <si>
-    <t>A1K3</t>
-  </si>
-  <si>
-    <t>A2DS</t>
-  </si>
-  <si>
-    <t>A3MD</t>
-  </si>
-  <si>
-    <t>A3MR</t>
-  </si>
-  <si>
-    <t>A2C6</t>
-  </si>
-  <si>
-    <t>A2DQ</t>
-  </si>
-  <si>
-    <t>A337</t>
-  </si>
-  <si>
-    <t>G697</t>
+    <t>A3MZ</t>
   </si>
   <si>
     <t>A3MC</t>
   </si>
   <si>
-    <t>A3MZ</t>
-  </si>
-  <si>
-    <t>A3NO</t>
-  </si>
-  <si>
-    <t>A3OL</t>
-  </si>
-  <si>
-    <t>A0AF</t>
-  </si>
-  <si>
-    <t>A31F</t>
-  </si>
-  <si>
-    <t>A3MT</t>
-  </si>
-  <si>
-    <t>H632</t>
-  </si>
-  <si>
-    <t>A0BB</t>
-  </si>
-  <si>
-    <t>I304</t>
-  </si>
-  <si>
-    <t>B884</t>
-  </si>
-  <si>
-    <t>D954</t>
-  </si>
-  <si>
-    <t>E483</t>
-  </si>
-  <si>
-    <t>G961</t>
-  </si>
-  <si>
-    <t>A2C5</t>
-  </si>
-  <si>
-    <t>A2BR</t>
-  </si>
-  <si>
-    <t>C346</t>
+    <t>A3I8</t>
+  </si>
+  <si>
+    <t>A607</t>
+  </si>
+  <si>
+    <t>I384</t>
   </si>
   <si>
     <t>B221</t>
   </si>
   <si>
-    <t>I384</t>
-  </si>
-  <si>
-    <t>A3I8</t>
-  </si>
-  <si>
-    <t>A607</t>
+    <t>A3J1</t>
+  </si>
+  <si>
+    <t>A3IC</t>
+  </si>
+  <si>
+    <t>A3KD</t>
+  </si>
+  <si>
+    <t>F290</t>
   </si>
   <si>
     <t>A35Y</t>
   </si>
   <si>
+    <t>E568</t>
+  </si>
+  <si>
     <t>A3LD</t>
   </si>
   <si>
-    <t>F290</t>
-  </si>
-  <si>
-    <t>A3KD</t>
-  </si>
-  <si>
     <t>A3WC</t>
   </si>
   <si>
     <t>E530</t>
   </si>
   <si>
-    <t>A3J1</t>
-  </si>
-  <si>
-    <t>E568</t>
-  </si>
-  <si>
-    <t>A3IC</t>
-  </si>
-  <si>
     <t>F497</t>
   </si>
   <si>
     <t>A2YJ</t>
   </si>
   <si>
+    <t>A10D</t>
+  </si>
+  <si>
     <t>G963</t>
   </si>
   <si>
+    <t>I305</t>
+  </si>
+  <si>
     <t>B896</t>
   </si>
   <si>
-    <t>I305</t>
+    <t>A20A</t>
   </si>
   <si>
     <t>B567</t>
   </si>
   <si>
-    <t>A20A</t>
-  </si>
-  <si>
     <t>E835</t>
   </si>
   <si>
+    <t>D619</t>
+  </si>
+  <si>
+    <t>B313</t>
+  </si>
+  <si>
+    <t>A3IF</t>
+  </si>
+  <si>
+    <t>E893</t>
+  </si>
+  <si>
+    <t>A400</t>
+  </si>
+  <si>
+    <t>D576</t>
+  </si>
+  <si>
+    <t>E660</t>
+  </si>
+  <si>
+    <t>A235</t>
+  </si>
+  <si>
+    <t>E791</t>
+  </si>
+  <si>
+    <t>A1OP</t>
+  </si>
+  <si>
+    <t>A32C</t>
+  </si>
+  <si>
+    <t>A278</t>
+  </si>
+  <si>
+    <t>A719</t>
+  </si>
+  <si>
     <t>A3QL</t>
   </si>
   <si>
-    <t>A400</t>
-  </si>
-  <si>
-    <t>A32C</t>
-  </si>
-  <si>
-    <t>A719</t>
-  </si>
-  <si>
-    <t>A235</t>
-  </si>
-  <si>
     <t>H115</t>
   </si>
   <si>
-    <t>E893</t>
-  </si>
-  <si>
-    <t>D576</t>
-  </si>
-  <si>
-    <t>E660</t>
-  </si>
-  <si>
-    <t>A278</t>
-  </si>
-  <si>
-    <t>D619</t>
-  </si>
-  <si>
-    <t>A3IF</t>
-  </si>
-  <si>
-    <t>A1OP</t>
-  </si>
-  <si>
-    <t>E791</t>
+    <t>A3TC</t>
+  </si>
+  <si>
+    <t>A4HG</t>
+  </si>
+  <si>
+    <t>A3TD</t>
+  </si>
+  <si>
+    <t>E721</t>
+  </si>
+  <si>
+    <t>H173</t>
+  </si>
+  <si>
+    <t>A3RR</t>
+  </si>
+  <si>
+    <t>A3TF</t>
+  </si>
+  <si>
+    <t>A3X5</t>
+  </si>
+  <si>
+    <t>A4FO</t>
+  </si>
+  <si>
+    <t>A4FN</t>
+  </si>
+  <si>
+    <t>F959</t>
   </si>
   <si>
     <t>A2CR</t>
@@ -223,73 +262,58 @@
     <t>A4I4</t>
   </si>
   <si>
-    <t>A4HG</t>
-  </si>
-  <si>
-    <t>A4FN</t>
-  </si>
-  <si>
-    <t>A3TF</t>
-  </si>
-  <si>
-    <t>F959</t>
-  </si>
-  <si>
-    <t>A3X5</t>
-  </si>
-  <si>
-    <t>A3TC</t>
-  </si>
-  <si>
     <t>A2CT</t>
   </si>
   <si>
-    <t>E721</t>
-  </si>
-  <si>
-    <t>H173</t>
-  </si>
-  <si>
-    <t>A3TD</t>
-  </si>
-  <si>
-    <t>A3RR</t>
-  </si>
-  <si>
     <t>A2FK</t>
   </si>
   <si>
     <t>J447</t>
   </si>
   <si>
-    <t>A4FO</t>
+    <t>A0ZE</t>
+  </si>
+  <si>
+    <t>A1PM</t>
+  </si>
+  <si>
+    <t>A399</t>
+  </si>
+  <si>
+    <t>G730</t>
   </si>
   <si>
     <t>E190</t>
   </si>
   <si>
-    <t>A0ZE</t>
-  </si>
-  <si>
-    <t>G730</t>
-  </si>
-  <si>
-    <t>A1PM</t>
+    <t>A41Z</t>
+  </si>
+  <si>
+    <t>A3RO</t>
+  </si>
+  <si>
+    <t>A3PS</t>
+  </si>
+  <si>
+    <t>A44H</t>
+  </si>
+  <si>
+    <t>A3UU</t>
+  </si>
+  <si>
+    <t>H439</t>
+  </si>
+  <si>
+    <t>A3IY</t>
   </si>
   <si>
     <t>A3O3</t>
   </si>
   <si>
-    <t>A3IY</t>
-  </si>
-  <si>
-    <t>A3RO</t>
-  </si>
-  <si>
     <t>D259</t>
   </si>
   <si>
-    <t>A3UU</t>
+    <t>A2IE</t>
   </si>
   <si>
     <t>A2I3</t>
@@ -298,163 +322,151 @@
     <t>A30J</t>
   </si>
   <si>
+    <t>H681</t>
+  </si>
+  <si>
     <t>A2PL</t>
   </si>
   <si>
-    <t>A41Z</t>
-  </si>
-  <si>
-    <t>H439</t>
-  </si>
-  <si>
-    <t>A44H</t>
-  </si>
-  <si>
-    <t>A3PS</t>
-  </si>
-  <si>
-    <t>H681</t>
-  </si>
-  <si>
-    <t>A2IE</t>
-  </si>
-  <si>
     <t>C216</t>
   </si>
   <si>
     <t>A3KP</t>
   </si>
   <si>
+    <t>B622</t>
+  </si>
+  <si>
     <t>A3KA</t>
   </si>
   <si>
-    <t>B622</t>
+    <t>A3RQ</t>
   </si>
   <si>
     <t>A3KO</t>
   </si>
   <si>
-    <t>A3RQ</t>
+    <t>A3JQ</t>
+  </si>
+  <si>
+    <t>A3NK</t>
+  </si>
+  <si>
+    <t>I588</t>
+  </si>
+  <si>
+    <t>A0TT</t>
+  </si>
+  <si>
+    <t>A3UF</t>
   </si>
   <si>
     <t>A3YI</t>
   </si>
   <si>
+    <t>A41F</t>
+  </si>
+  <si>
     <t>A3YZ</t>
   </si>
   <si>
     <t>A3TU</t>
   </si>
   <si>
-    <t>A3NK</t>
-  </si>
-  <si>
-    <t>A3UF</t>
-  </si>
-  <si>
-    <t>I588</t>
-  </si>
-  <si>
-    <t>A0TT</t>
-  </si>
-  <si>
-    <t>A41F</t>
-  </si>
-  <si>
-    <t>A3JQ</t>
+    <t>A3ZB</t>
+  </si>
+  <si>
+    <t>A3HH</t>
+  </si>
+  <si>
+    <t>A3ZE</t>
+  </si>
+  <si>
+    <t>A1H9</t>
+  </si>
+  <si>
+    <t>C913</t>
+  </si>
+  <si>
+    <t>A3J4</t>
+  </si>
+  <si>
+    <t>A3ZC</t>
   </si>
   <si>
     <t>A0GZ</t>
   </si>
   <si>
+    <t>A3U8</t>
+  </si>
+  <si>
+    <t>A3Z9</t>
+  </si>
+  <si>
+    <t>A0G6</t>
+  </si>
+  <si>
+    <t>A3TV</t>
+  </si>
+  <si>
+    <t>F766</t>
+  </si>
+  <si>
+    <t>A3YK</t>
+  </si>
+  <si>
+    <t>A0LX</t>
+  </si>
+  <si>
+    <t>A4AB</t>
+  </si>
+  <si>
+    <t>C926</t>
+  </si>
+  <si>
+    <t>A3GV</t>
+  </si>
+  <si>
+    <t>A2JX</t>
+  </si>
+  <si>
+    <t>A0GT</t>
+  </si>
+  <si>
     <t>A3YQ</t>
   </si>
   <si>
-    <t>A3YK</t>
-  </si>
-  <si>
-    <t>A3Z9</t>
-  </si>
-  <si>
-    <t>A3U8</t>
-  </si>
-  <si>
-    <t>A0LX</t>
-  </si>
-  <si>
-    <t>A3ZE</t>
-  </si>
-  <si>
     <t>B2UZ</t>
   </si>
   <si>
-    <t>A3GV</t>
-  </si>
-  <si>
-    <t>A3HH</t>
-  </si>
-  <si>
-    <t>A3J4</t>
-  </si>
-  <si>
-    <t>A0G6</t>
-  </si>
-  <si>
-    <t>A3TV</t>
-  </si>
-  <si>
-    <t>A3ZB</t>
-  </si>
-  <si>
-    <t>F766</t>
-  </si>
-  <si>
     <t>A0G5</t>
   </si>
   <si>
-    <t>A3ZC</t>
-  </si>
-  <si>
-    <t>A0GT</t>
-  </si>
-  <si>
-    <t>A2JX</t>
-  </si>
-  <si>
-    <t>A4AB</t>
-  </si>
-  <si>
-    <t>C926</t>
-  </si>
-  <si>
-    <t>A1H9</t>
-  </si>
-  <si>
-    <t>C913</t>
+    <t>C213</t>
   </si>
   <si>
     <t>A1ZD</t>
   </si>
   <si>
-    <t>C213</t>
+    <t>A0G7</t>
   </si>
   <si>
     <t>A3YU</t>
   </si>
   <si>
+    <t>A3YM</t>
+  </si>
+  <si>
+    <t>A3Z2</t>
+  </si>
+  <si>
+    <t>A4DU</t>
+  </si>
+  <si>
     <t>A515</t>
   </si>
   <si>
-    <t>A4DU</t>
-  </si>
-  <si>
-    <t>A0G7</t>
-  </si>
-  <si>
-    <t>A3Z2</t>
-  </si>
-  <si>
-    <t>A3YM</t>
+    <t>I345</t>
   </si>
   <si>
     <t>A2FA</t>
@@ -463,112 +475,109 @@
     <t>A2HX</t>
   </si>
   <si>
-    <t>I345</t>
+    <t>A3OQ</t>
   </si>
   <si>
     <t>B366</t>
   </si>
   <si>
-    <t>A3OQ</t>
-  </si>
-  <si>
     <t>F012</t>
   </si>
   <si>
+    <t>A3OR</t>
+  </si>
+  <si>
     <t>A4CZ</t>
   </si>
   <si>
-    <t>A3OR</t>
+    <t>A4AJ</t>
+  </si>
+  <si>
+    <t>A4AO</t>
   </si>
   <si>
     <t>A34P</t>
   </si>
   <si>
+    <t>A4AL</t>
+  </si>
+  <si>
+    <t>A4CF</t>
+  </si>
+  <si>
+    <t>G024</t>
+  </si>
+  <si>
+    <t>A37Y</t>
+  </si>
+  <si>
     <t>A2WI</t>
   </si>
   <si>
-    <t>A4AJ</t>
-  </si>
-  <si>
-    <t>A4AL</t>
-  </si>
-  <si>
-    <t>A4AO</t>
-  </si>
-  <si>
-    <t>A4CF</t>
-  </si>
-  <si>
-    <t>A37Y</t>
-  </si>
-  <si>
-    <t>G024</t>
+    <t>G046</t>
+  </si>
+  <si>
+    <t>A2O5</t>
   </si>
   <si>
     <t>A0BO</t>
   </si>
   <si>
-    <t>G046</t>
-  </si>
-  <si>
-    <t>A2O5</t>
+    <t>A3ON</t>
+  </si>
+  <si>
+    <t>A3S7</t>
+  </si>
+  <si>
+    <t>C947</t>
+  </si>
+  <si>
+    <t>A2GD</t>
+  </si>
+  <si>
+    <t>A0J5</t>
   </si>
   <si>
     <t>A3PR</t>
   </si>
   <si>
-    <t>C947</t>
-  </si>
-  <si>
-    <t>A3S7</t>
-  </si>
-  <si>
-    <t>A3ON</t>
-  </si>
-  <si>
-    <t>A0J5</t>
-  </si>
-  <si>
-    <t>A2GD</t>
+    <t>H146</t>
   </si>
   <si>
     <t>A3O6</t>
   </si>
   <si>
-    <t>H146</t>
-  </si>
-  <si>
     <t>A173</t>
   </si>
   <si>
+    <t>H094</t>
+  </si>
+  <si>
+    <t>A3TW</t>
+  </si>
+  <si>
+    <t>A11G</t>
+  </si>
+  <si>
     <t>A3TY</t>
   </si>
   <si>
-    <t>H094</t>
-  </si>
-  <si>
     <t>A3TX</t>
   </si>
   <si>
-    <t>A11G</t>
-  </si>
-  <si>
-    <t>A3TW</t>
-  </si>
-  <si>
     <t>A415</t>
   </si>
   <si>
+    <t>A393</t>
+  </si>
+  <si>
     <t>A2ST</t>
   </si>
   <si>
-    <t>A393</t>
+    <t>D575</t>
   </si>
   <si>
     <t>A3MB</t>
-  </si>
-  <si>
-    <t>D575</t>
   </si>
   <si>
     <t>start_punchtime</t>
@@ -1144,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J211"/>
+  <dimension ref="A1:J214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -1163,31 +1172,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1195,23 +1204,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46027.3309837963</v>
+        <v>46027.33467592593</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D2" s="2">
-        <v>46027.69519675926</v>
+        <v>46027.69517361111</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G2" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G2" s="2"/>
       <c r="H2" s="2">
         <v>0</v>
       </c>
@@ -1219,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1227,23 +1234,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>46027.28609953704</v>
+        <v>46027.32314814815</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D3" s="2">
-        <v>46027.70400462963</v>
+        <v>46027.69453703704</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" s="2">
-        <v>20.7</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G3" s="2"/>
       <c r="H3" s="2">
         <v>0</v>
       </c>
@@ -1251,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1259,23 +1264,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>46027.32351851852</v>
+        <v>46027.29700231482</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D4" s="2">
-        <v>46027.70342592592</v>
+        <v>46027.69305555556</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G4" s="2"/>
       <c r="H4" s="2">
         <v>0</v>
       </c>
@@ -1283,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1291,23 +1294,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>46027.32939814815</v>
+        <v>46027.32886574074</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D5" s="2">
-        <v>46027.69216435185</v>
+        <v>46027.7053125</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G5" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G5" s="2"/>
       <c r="H5" s="2">
         <v>0</v>
       </c>
@@ -1315,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1323,23 +1324,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>46027.32746527778</v>
+        <v>46027.32686342593</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D6" s="2">
-        <v>46027.70350694445</v>
+        <v>46027.69398148148</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G6" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G6" s="2"/>
       <c r="H6" s="2">
         <v>0</v>
       </c>
@@ -1347,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1355,23 +1354,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>46027.32314814815</v>
+        <v>46027.32302083333</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D7" s="2">
-        <v>46027.69453703704</v>
+        <v>46027.70119212963</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G7" s="2">
-        <v>18.7</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G7" s="2"/>
       <c r="H7" s="2">
         <v>0</v>
       </c>
@@ -1379,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1387,23 +1384,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>46027.33038194444</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D8" s="2">
-        <v>46027.69648148148</v>
+        <v>46027.70427083333</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G8" s="2">
-        <v>18.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G8" s="2"/>
       <c r="H8" s="2">
         <v>0</v>
       </c>
@@ -1411,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1419,23 +1414,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.32181712963</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D9" s="2">
-        <v>46027.70737268519</v>
+        <v>46027.70118055555</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9" s="2">
-        <v>18.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G9" s="2"/>
       <c r="H9" s="2">
         <v>0</v>
       </c>
@@ -1443,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1451,23 +1444,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>46027.3322800926</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D10" s="2">
-        <v>46027.68527777777</v>
+        <v>46027.69825231482</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G10" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G10" s="2"/>
       <c r="H10" s="2">
         <v>0</v>
       </c>
@@ -1475,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1483,23 +1474,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>46027.32505787037</v>
+        <v>46027.29821759259</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D11" s="2">
-        <v>46027.69226851852</v>
+        <v>46027.72569444445</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G11" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="2">
         <v>0</v>
       </c>
@@ -1507,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1515,23 +1504,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>46027.32686342593</v>
+        <v>46027.3309837963</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D12" s="2">
-        <v>46027.69398148148</v>
+        <v>46027.69519675926</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G12" s="2">
-        <v>18.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G12" s="2"/>
       <c r="H12" s="2">
         <v>0</v>
       </c>
@@ -1539,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1547,23 +1534,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>46027.32886574074</v>
+        <v>46027.33130787037</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D13" s="2">
-        <v>46027.7053125</v>
+        <v>46027.69548611111</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" s="2">
-        <v>18.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G13" s="2"/>
       <c r="H13" s="2">
         <v>0</v>
       </c>
@@ -1571,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1579,23 +1564,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>46027.33467592593</v>
+        <v>46027.33116898148</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D14" s="2">
-        <v>46027.69517361111</v>
+        <v>46027.69346064814</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G14" s="2">
-        <v>18.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G14" s="2"/>
       <c r="H14" s="2">
         <v>0</v>
       </c>
@@ -1603,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1611,23 +1594,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>46027.29700231482</v>
+        <v>46027.3419212963</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D15" s="2">
-        <v>46027.69305555556</v>
+        <v>46027.69234953704</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G15" s="2">
-        <v>20.7</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G15" s="2"/>
       <c r="H15" s="2">
         <v>0</v>
       </c>
@@ -1635,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1643,23 +1624,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>46027.33186342593</v>
+        <v>46027.33445601852</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D16" s="2">
-        <v>46027.69719907407</v>
+        <v>46027.71418981482</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G16" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G16" s="2"/>
       <c r="H16" s="2">
         <v>0</v>
       </c>
@@ -1667,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1675,23 +1654,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>46027.33789351852</v>
+        <v>46027.32319444444</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D17" s="2">
-        <v>46027.70591435185</v>
+        <v>46027.70380787037</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G17" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G17" s="2"/>
       <c r="H17" s="2">
         <v>0</v>
       </c>
@@ -1699,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1707,23 +1684,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>46027.32311342593</v>
+        <v>46027.28609953704</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D18" s="2">
-        <v>46027.6875</v>
+        <v>46027.70400462963</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G18" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G18" s="2"/>
       <c r="H18" s="2">
         <v>0</v>
       </c>
@@ -1731,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1739,23 +1714,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.32351851852</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D19" s="2">
-        <v>46027.6928125</v>
+        <v>46027.70342592592</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G19" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G19" s="2"/>
       <c r="H19" s="2">
         <v>0</v>
       </c>
@@ -1763,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1771,23 +1744,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>46027.3419212963</v>
+        <v>46027.32939814815</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D20" s="2">
-        <v>46027.69234953704</v>
+        <v>46027.69216435185</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G20" s="2">
-        <v>18.7</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G20" s="2"/>
       <c r="H20" s="2">
         <v>0</v>
       </c>
@@ -1795,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1803,23 +1774,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>46027.33445601852</v>
+        <v>46027.27918981481</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D21" s="2">
-        <v>46027.71418981482</v>
+        <v>46027.71783564815</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G21" s="2">
-        <v>18.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G21" s="2"/>
       <c r="H21" s="2">
         <v>0</v>
       </c>
@@ -1827,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1835,23 +1804,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>46027.32319444444</v>
+        <v>46027.3322800926</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D22" s="2">
-        <v>46027.70380787037</v>
+        <v>46027.68527777777</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G22" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G22" s="2"/>
       <c r="H22" s="2">
         <v>0</v>
       </c>
@@ -1859,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1867,23 +1834,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>46027.27918981481</v>
+        <v>46027.33038194444</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D23" s="2">
-        <v>46027.71783564815</v>
+        <v>46027.69648148148</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G23" s="2">
-        <v>26.8</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G23" s="2"/>
       <c r="H23" s="2">
         <v>0</v>
       </c>
@@ -1891,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1899,23 +1864,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>46027.33277777778</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D24" s="2">
-        <v>46027.69575231482</v>
+        <v>46027.70737268519</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G24" s="2">
-        <v>18.7</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G24" s="2"/>
       <c r="H24" s="2">
         <v>0</v>
       </c>
@@ -1923,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1931,19 +1894,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>46027.29821759259</v>
+        <v>46027.32505787037</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D25" s="2">
+        <v>46027.69226851852</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F25" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G25" s="2">
-        <v>23</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G25" s="2"/>
       <c r="H25" s="2">
         <v>0</v>
       </c>
@@ -1951,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1959,23 +1924,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.33277777778</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D26" s="2">
-        <v>46027.69825231482</v>
+        <v>46027.69575231482</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G26" s="2">
-        <v>18.7</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G26" s="2"/>
       <c r="H26" s="2">
         <v>0</v>
       </c>
@@ -1983,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1991,23 +1954,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>46027.32181712963</v>
+        <v>46027.33438657408</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D27" s="2">
-        <v>46027.70118055555</v>
+        <v>46027.69641203704</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G27" s="2">
-        <v>19.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G27" s="2"/>
       <c r="H27" s="2">
         <v>0</v>
       </c>
@@ -2015,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2026,20 +1987,18 @@
         <v>46027.33333333334</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D28" s="2">
-        <v>46027.70427083333</v>
+        <v>46027.6928125</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G28" s="2">
-        <v>18.35</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G28" s="2"/>
       <c r="H28" s="2">
         <v>0</v>
       </c>
@@ -2047,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2055,23 +2014,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>46027.32302083333</v>
+        <v>46027.32311342593</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D29" s="2">
-        <v>46027.70119212963</v>
+        <v>46027.6875</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G29" s="2">
-        <v>19.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G29" s="2"/>
       <c r="H29" s="2">
         <v>0</v>
       </c>
@@ -2079,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2087,23 +2044,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>46027.33116898148</v>
+        <v>46027.32746527778</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D30" s="2">
-        <v>46027.69346064814</v>
+        <v>46027.70350694445</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G30" s="2">
-        <v>18.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G30" s="2"/>
       <c r="H30" s="2">
         <v>0</v>
       </c>
@@ -2111,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2119,23 +2074,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>46027.33130787037</v>
+        <v>46027.33789351852</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D31" s="2">
-        <v>46027.69548611111</v>
+        <v>46027.70591435185</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G31" s="2">
-        <v>18.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G31" s="2"/>
       <c r="H31" s="2">
         <v>0</v>
       </c>
@@ -2143,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2151,23 +2104,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>46027.33438657408</v>
+        <v>46027.33186342593</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D32" s="2">
-        <v>46027.69641203704</v>
+        <v>46027.69719907407</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G32" s="2">
-        <v>19.6</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G32" s="2"/>
       <c r="H32" s="2">
         <v>0</v>
       </c>
@@ -2175,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2183,23 +2134,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>46027.26914351852</v>
+        <v>46027.26454861111</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D33" s="2">
-        <v>46027.73650462963</v>
+        <v>46027.7358912037</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G33" s="2">
-        <v>27</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="G33" s="2"/>
       <c r="H33" s="2">
         <v>0</v>
       </c>
@@ -2207,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2215,23 +2164,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>46027.27104166667</v>
+        <v>46027.27672453703</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D34" s="2">
-        <v>46027.72087962963</v>
+        <v>46027.72111111111</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G34" s="2">
-        <v>27</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="G34" s="2"/>
       <c r="H34" s="2">
         <v>0</v>
       </c>
@@ -2239,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2247,23 +2194,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>46027.26454861111</v>
+        <v>46027.27104166667</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D35" s="2">
-        <v>46027.7358912037</v>
+        <v>46027.72087962963</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G35" s="2">
-        <v>22.4</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="G35" s="2"/>
       <c r="H35" s="2">
         <v>0</v>
       </c>
@@ -2271,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2279,23 +2224,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>46027.27672453703</v>
+        <v>46027.26914351852</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D36" s="2">
-        <v>46027.72111111111</v>
+        <v>46027.73650462963</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G36" s="2">
-        <v>20.2</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="G36" s="2"/>
       <c r="H36" s="2">
         <v>0</v>
       </c>
@@ -2303,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2311,23 +2254,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>46027.00646990741</v>
+        <v>46027.57959490741</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D37" s="2">
-        <v>46027.41113425926</v>
+        <v>46028.00751157408</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G37" s="2">
-        <v>19.65</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G37" s="2"/>
       <c r="H37" s="2">
         <v>0</v>
       </c>
@@ -2335,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2343,23 +2284,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>46027.01200231481</v>
+        <v>46027.58938657407</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D38" s="2">
-        <v>46027.44277777777</v>
+        <v>46027.78034722222</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G38" s="2">
-        <v>20.2</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G38" s="2"/>
       <c r="H38" s="2">
         <v>0</v>
       </c>
@@ -2367,27 +2306,29 @@
         <v>0</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>46027.99134259259</v>
+        <v>46027.57675925926</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D39" s="2">
+        <v>46028.01075231482</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F39" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G39" s="2">
-        <v>20.2</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G39" s="2"/>
       <c r="H39" s="2">
         <v>0</v>
       </c>
@@ -2395,31 +2336,29 @@
         <v>0</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2">
         <v>46027.58105324074</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D40" s="2">
         <v>46028.02493055556</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G40" s="2">
-        <v>25.7</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G40" s="2"/>
       <c r="H40" s="2">
         <v>0</v>
       </c>
@@ -2427,30 +2366,30 @@
         <v>0</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>46027.57675925926</v>
+        <v>46027.00646990741</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D41" s="2">
-        <v>46028.01075231482</v>
+        <v>46027.41113425926</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G41" s="2">
-        <v>20.2</v>
+        <v>19.65</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -2459,27 +2398,29 @@
         <v>0</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>46027.99311342592</v>
+        <v>46027.28767361111</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D42" s="2">
+        <v>46027.73832175926</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F42" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G42" s="2">
-        <v>20.2</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G42" s="2"/>
       <c r="H42" s="2">
         <v>0</v>
       </c>
@@ -2487,27 +2428,29 @@
         <v>0</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>46027.99076388889</v>
+        <v>46027.99134259259</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D43" s="2">
+        <v>46028.34385416667</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F43" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G43" s="2">
-        <v>20.2</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G43" s="2"/>
       <c r="H43" s="2">
         <v>0</v>
       </c>
@@ -2515,31 +2458,29 @@
         <v>0</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>46027.57959490741</v>
+        <v>46027.99311342592</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D44" s="2">
-        <v>46028.00751157408</v>
+        <v>46028.45871527777</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G44" s="2">
-        <v>20.2</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G44" s="2"/>
       <c r="H44" s="2">
         <v>0</v>
       </c>
@@ -2547,31 +2488,29 @@
         <v>0</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>46027.28767361111</v>
+        <v>46027.99076388889</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D45" s="2">
-        <v>46027.73832175926</v>
+        <v>46028.53190972222</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G45" s="2">
-        <v>30.75</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G45" s="2"/>
       <c r="H45" s="2">
         <v>0</v>
       </c>
@@ -2579,31 +2518,29 @@
         <v>0</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B46" s="2">
-        <v>46027.58938657407</v>
+        <v>46027.01200231481</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D46" s="2">
-        <v>46027.78034722222</v>
+        <v>46027.44277777777</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G46" s="2">
-        <v>20.2</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G46" s="2"/>
       <c r="H46" s="2">
         <v>0</v>
       </c>
@@ -2611,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2619,23 +2556,21 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>46027.07840277778</v>
+        <v>46027.91351851852</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D47" s="2">
-        <v>46027.41340277778</v>
+        <v>46028.14635416667</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G47" s="2">
-        <v>25</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="G47" s="2"/>
       <c r="H47" s="2">
         <v>0</v>
       </c>
@@ -2643,30 +2578,30 @@
         <v>0</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>46027.91351851852</v>
+        <v>46027.32765046296</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D48" s="2">
-        <v>46028.14635416667</v>
+        <v>46027.7409375</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G48" s="2">
-        <v>25</v>
+        <v>17.85</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -2675,31 +2610,29 @@
         <v>0</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" s="2">
-        <v>46027.32765046296</v>
+        <v>46027.07840277778</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D49" s="2">
-        <v>46027.7409375</v>
+        <v>46027.41340277778</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G49" s="2">
-        <v>17.85</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="G49" s="2"/>
       <c r="H49" s="2">
         <v>0</v>
       </c>
@@ -2707,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2715,19 +2648,21 @@
         <v>47</v>
       </c>
       <c r="B50" s="2">
-        <v>46027.69027777778</v>
+        <v>46027.32430555556</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D50" s="2">
+        <v>46027.74112268518</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F50" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G50" s="2">
-        <v>23</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="G50" s="2"/>
       <c r="H50" s="2">
         <v>0</v>
       </c>
@@ -2735,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2743,23 +2678,21 @@
         <v>48</v>
       </c>
       <c r="B51" s="2">
-        <v>46027.68099537037</v>
+        <v>46027.69027777778</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D51" s="2">
-        <v>46027.88957175926</v>
+        <v>46027.9375</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G51" s="2">
-        <v>17</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="G51" s="2"/>
       <c r="H51" s="2">
         <v>0</v>
       </c>
@@ -2767,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2778,20 +2711,18 @@
         <v>46027.38194444445</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D52" s="2">
         <v>46027.38201388889</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G52" s="2">
-        <v>20.7</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="G52" s="2"/>
       <c r="H52" s="2">
         <v>0</v>
       </c>
@@ -2799,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2807,22 +2738,22 @@
         <v>50</v>
       </c>
       <c r="B53" s="2">
-        <v>46027.289375</v>
+        <v>46027.68099537037</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D53" s="2">
-        <v>46027.52762731481</v>
+        <v>46027.88957175926</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G53" s="2">
-        <v>35.5</v>
+        <v>17</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -2831,31 +2762,29 @@
         <v>0</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" s="2">
-        <v>46027.54813657407</v>
+        <v>46027.33201388889</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D54" s="2">
-        <v>46027.66322916667</v>
+        <v>46027.50045138889</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G54" s="2">
-        <v>35.5</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G54" s="2"/>
       <c r="H54" s="2">
         <v>0</v>
       </c>
@@ -2863,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2871,23 +2800,21 @@
         <v>51</v>
       </c>
       <c r="B55" s="2">
-        <v>46027.33201388889</v>
+        <v>46027.52120370371</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D55" s="2">
-        <v>46027.50045138889</v>
+        <v>46027.72983796296</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G55" s="2">
-        <v>40.5</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G55" s="2"/>
       <c r="H55" s="2">
         <v>0</v>
       </c>
@@ -2895,31 +2822,29 @@
         <v>0</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B56" s="2">
-        <v>46027.52120370371</v>
+        <v>46027.54813657407</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D56" s="2">
-        <v>46027.72983796296</v>
+        <v>46027.66322916667</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G56" s="2">
-        <v>40.5</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G56" s="2"/>
       <c r="H56" s="2">
         <v>0</v>
       </c>
@@ -2927,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2935,23 +2860,21 @@
         <v>52</v>
       </c>
       <c r="B57" s="2">
-        <v>46027.31453703704</v>
+        <v>46027.289375</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D57" s="2">
-        <v>46027.72277777778</v>
+        <v>46027.52762731481</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G57" s="2">
-        <v>23.35</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G57" s="2"/>
       <c r="H57" s="2">
         <v>0</v>
       </c>
@@ -2959,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2967,19 +2890,21 @@
         <v>53</v>
       </c>
       <c r="B58" s="2">
-        <v>46027.32267361111</v>
+        <v>46027.31453703704</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D58" s="2">
+        <v>46027.72277777778</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F58" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G58" s="2">
-        <v>20.2</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G58" s="2"/>
       <c r="H58" s="2">
         <v>0</v>
       </c>
@@ -2987,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2995,23 +2920,21 @@
         <v>54</v>
       </c>
       <c r="B59" s="2">
-        <v>46027.32479166667</v>
+        <v>46027.31934027778</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D59" s="2">
-        <v>46027.7072800926</v>
+        <v>46027.72951388889</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G59" s="2">
-        <v>23.35</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G59" s="2"/>
       <c r="H59" s="2">
         <v>0</v>
       </c>
@@ -3019,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -3027,31 +2950,29 @@
         <v>55</v>
       </c>
       <c r="B60" s="2">
-        <v>46027.31788194444</v>
+        <v>46027.5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D60" s="2">
-        <v>46027.72849537037</v>
+        <v>46027.5</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G60" s="2">
-        <v>19.6</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G60" s="2"/>
       <c r="H60" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I60" s="2">
         <v>0</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -3059,23 +2980,21 @@
         <v>56</v>
       </c>
       <c r="B61" s="2">
-        <v>46027.32268518519</v>
+        <v>46027.32181712963</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D61" s="2">
-        <v>46027.7158912037</v>
+        <v>46027.729375</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G61" s="2">
-        <v>23.35</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G61" s="2"/>
       <c r="H61" s="2">
         <v>0</v>
       </c>
@@ -3083,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -3091,23 +3010,21 @@
         <v>57</v>
       </c>
       <c r="B62" s="2">
-        <v>46027.32813657408</v>
+        <v>46027.3253125</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D62" s="2">
-        <v>46027.72304398148</v>
+        <v>46027.73775462963</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G62" s="2">
-        <v>22.4</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G62" s="2"/>
       <c r="H62" s="2">
         <v>0</v>
       </c>
@@ -3115,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -3123,23 +3040,21 @@
         <v>58</v>
       </c>
       <c r="B63" s="2">
-        <v>46027.31282407408</v>
+        <v>46027.32479166667</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D63" s="2">
-        <v>46027.72940972223</v>
+        <v>46027.7072800926</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G63" s="2">
-        <v>23.85</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G63" s="2"/>
       <c r="H63" s="2">
         <v>0</v>
       </c>
@@ -3147,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -3155,23 +3070,21 @@
         <v>59</v>
       </c>
       <c r="B64" s="2">
-        <v>46027.3253125</v>
+        <v>46027.32150462963</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D64" s="2">
-        <v>46027.73775462963</v>
+        <v>46027.72916666666</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G64" s="2">
-        <v>22.4</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G64" s="2"/>
       <c r="H64" s="2">
         <v>0</v>
       </c>
@@ -3179,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -3187,19 +3100,21 @@
         <v>60</v>
       </c>
       <c r="B65" s="2">
-        <v>46027.32150462963</v>
+        <v>46027.32239583333</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D65" s="2">
+        <v>46027.7265162037</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F65" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G65" s="2">
-        <v>23</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G65" s="2"/>
       <c r="H65" s="2">
         <v>0</v>
       </c>
@@ -3207,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -3215,23 +3130,21 @@
         <v>61</v>
       </c>
       <c r="B66" s="2">
-        <v>46027.32239583333</v>
+        <v>46027.32813657408</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D66" s="2">
-        <v>46027.7265162037</v>
+        <v>46027.72304398148</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G66" s="2">
-        <v>20.95</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G66" s="2"/>
       <c r="H66" s="2">
         <v>0</v>
       </c>
@@ -3239,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -3247,23 +3160,21 @@
         <v>62</v>
       </c>
       <c r="B67" s="2">
-        <v>46027.31940972222</v>
+        <v>46027.31929398148</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D67" s="2">
-        <v>46027.73296296296</v>
+        <v>46027.73099537037</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G67" s="2">
-        <v>20.95</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G67" s="2"/>
       <c r="H67" s="2">
         <v>0</v>
       </c>
@@ -3271,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -3279,23 +3190,21 @@
         <v>63</v>
       </c>
       <c r="B68" s="2">
-        <v>46027.31934027778</v>
+        <v>46027.52685185185</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D68" s="2">
-        <v>46027.72951388889</v>
+        <v>46027.72938657407</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G68" s="2">
-        <v>23.85</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G68" s="2"/>
       <c r="H68" s="2">
         <v>0</v>
       </c>
@@ -3303,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -3311,23 +3220,21 @@
         <v>64</v>
       </c>
       <c r="B69" s="2">
-        <v>46027.32181712963</v>
+        <v>46027.31788194444</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D69" s="2">
-        <v>46027.729375</v>
+        <v>46027.72849537037</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G69" s="2">
-        <v>20.2</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G69" s="2"/>
       <c r="H69" s="2">
         <v>0</v>
       </c>
@@ -3335,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -3343,23 +3250,21 @@
         <v>65</v>
       </c>
       <c r="B70" s="2">
-        <v>46027.52685185185</v>
+        <v>46027.31940972222</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D70" s="2">
-        <v>46027.72938657407</v>
+        <v>46027.73296296296</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G70" s="2">
-        <v>20.7</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G70" s="2"/>
       <c r="H70" s="2">
         <v>0</v>
       </c>
@@ -3367,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3375,23 +3280,21 @@
         <v>66</v>
       </c>
       <c r="B71" s="2">
-        <v>46027.31929398148</v>
+        <v>46027.32268518519</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D71" s="2">
-        <v>46027.73099537037</v>
+        <v>46027.7158912037</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G71" s="2">
-        <v>20.2</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G71" s="2"/>
       <c r="H71" s="2">
         <v>0</v>
       </c>
@@ -3399,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3407,23 +3310,21 @@
         <v>67</v>
       </c>
       <c r="B72" s="2">
-        <v>46027.3125</v>
+        <v>46027.32267361111</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D72" s="2">
-        <v>46027.72916666666</v>
+        <v>46027.71875</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G72" s="2">
-        <v>22.4</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G72" s="2"/>
       <c r="H72" s="2">
         <v>0</v>
       </c>
@@ -3431,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3439,23 +3340,21 @@
         <v>68</v>
       </c>
       <c r="B73" s="2">
-        <v>46027.31983796296</v>
+        <v>46027.31282407408</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D73" s="2">
-        <v>46027.54662037037</v>
+        <v>46027.72940972223</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G73" s="2">
-        <v>19.25</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G73" s="2"/>
       <c r="H73" s="2">
         <v>0</v>
       </c>
@@ -3463,27 +3362,29 @@
         <v>0</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B74" s="2">
-        <v>46027.55604166666</v>
+        <v>46027.32465277778</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D74" s="2">
+        <v>46027.48158564815</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F74" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G74" s="2">
-        <v>19.25</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G74" s="2"/>
       <c r="H74" s="2">
         <v>0</v>
       </c>
@@ -3491,31 +3392,29 @@
         <v>0</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B75" s="2">
         <v>46027.32167824074</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D75" s="2">
         <v>46027.61268518519</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G75" s="2">
-        <v>19.25</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G75" s="2"/>
       <c r="H75" s="2">
         <v>0</v>
       </c>
@@ -3523,31 +3422,29 @@
         <v>0</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B76" s="2">
-        <v>46027.29773148148</v>
+        <v>46027.34320601852</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D76" s="2">
-        <v>46027.47924768519</v>
+        <v>46027.69208333334</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G76" s="2">
-        <v>19.25</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G76" s="2"/>
       <c r="H76" s="2">
         <v>0</v>
       </c>
@@ -3555,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3563,23 +3460,17 @@
         <v>71</v>
       </c>
       <c r="B77" s="2">
-        <v>46027.3241550926</v>
+        <v>46027.69210648148</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D77" s="2">
-        <v>46027.60688657407</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>192</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G77" s="2">
-        <v>19.25</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G77" s="2"/>
       <c r="H77" s="2">
         <v>0</v>
       </c>
@@ -3587,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3595,23 +3486,21 @@
         <v>72</v>
       </c>
       <c r="B78" s="2">
-        <v>46027.33409722222</v>
+        <v>46027.40625</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D78" s="2">
-        <v>46027.53319444445</v>
+        <v>46027.66666666666</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G78" s="2">
-        <v>19.75</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G78" s="2"/>
       <c r="H78" s="2">
         <v>0</v>
       </c>
@@ -3619,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3627,22 +3516,22 @@
         <v>73</v>
       </c>
       <c r="B79" s="2">
-        <v>46027.33511574074</v>
+        <v>46027.39755787037</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D79" s="2">
-        <v>46027.78270833333</v>
+        <v>46027.66666666666</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G79" s="2">
-        <v>19.25</v>
+        <v>17.65</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3651,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3659,23 +3548,21 @@
         <v>74</v>
       </c>
       <c r="B80" s="2">
-        <v>46027.32465277778</v>
+        <v>46027.32547453704</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D80" s="2">
-        <v>46027.48158564815</v>
+        <v>46027.57592592593</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G80" s="2">
-        <v>19.25</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G80" s="2"/>
       <c r="H80" s="2">
         <v>0</v>
       </c>
@@ -3683,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3691,23 +3578,21 @@
         <v>75</v>
       </c>
       <c r="B81" s="2">
-        <v>46027.34802083333</v>
+        <v>46027.3241550926</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D81" s="2">
-        <v>46027.67233796296</v>
+        <v>46027.60688657407</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G81" s="2">
-        <v>19.6</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G81" s="2"/>
       <c r="H81" s="2">
         <v>0</v>
       </c>
@@ -3715,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3723,23 +3608,21 @@
         <v>76</v>
       </c>
       <c r="B82" s="2">
-        <v>46027.40625</v>
+        <v>46027.33511574074</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D82" s="2">
-        <v>46027.66666666666</v>
+        <v>46027.56944444445</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G82" s="2">
-        <v>19.6</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G82" s="2"/>
       <c r="H82" s="2">
         <v>0</v>
       </c>
@@ -3747,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3755,23 +3638,21 @@
         <v>77</v>
       </c>
       <c r="B83" s="2">
-        <v>46027.39755787037</v>
+        <v>46027.32111111111</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D83" s="2">
-        <v>46027.66666666666</v>
+        <v>46027.50440972222</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G83" s="2">
-        <v>17.65</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G83" s="2"/>
       <c r="H83" s="2">
         <v>0</v>
       </c>
@@ -3779,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3787,23 +3668,21 @@
         <v>78</v>
       </c>
       <c r="B84" s="2">
-        <v>46027.34320601852</v>
+        <v>46027.29773148148</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D84" s="2">
-        <v>46027.69208333334</v>
+        <v>46027.47924768519</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G84" s="2">
-        <v>19.25</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G84" s="2"/>
       <c r="H84" s="2">
         <v>0</v>
       </c>
@@ -3811,27 +3690,29 @@
         <v>0</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B85" s="2">
-        <v>46027.69210648148</v>
+        <v>46027.33409722222</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D85" s="2">
+        <v>46027.53319444445</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F85" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G85" s="2">
-        <v>19.25</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G85" s="2"/>
       <c r="H85" s="2">
         <v>0</v>
       </c>
@@ -3839,31 +3720,29 @@
         <v>0</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B86" s="2">
-        <v>46027.32547453704</v>
+        <v>46027.3125</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D86" s="2">
-        <v>46027.57592592593</v>
+        <v>46027.72916666666</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G86" s="2">
-        <v>19.25</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G86" s="2"/>
       <c r="H86" s="2">
         <v>0</v>
       </c>
@@ -3871,31 +3750,29 @@
         <v>0</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B87" s="2">
-        <v>46027.31991898148</v>
+        <v>46027.31983796296</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D87" s="2">
-        <v>46027.67479166666</v>
+        <v>46027.54662037037</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G87" s="2">
-        <v>19.6</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G87" s="2"/>
       <c r="H87" s="2">
         <v>0</v>
       </c>
@@ -3903,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -3911,23 +3788,21 @@
         <v>81</v>
       </c>
       <c r="B88" s="2">
-        <v>46027.33503472222</v>
+        <v>46027.55604166666</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D88" s="2">
-        <v>46027.66853009259</v>
+        <v>46027.67361111111</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G88" s="2">
-        <v>18.6</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G88" s="2"/>
       <c r="H88" s="2">
         <v>0</v>
       </c>
@@ -3935,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -3943,23 +3818,21 @@
         <v>82</v>
       </c>
       <c r="B89" s="2">
-        <v>46027.32111111111</v>
+        <v>46027.34802083333</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D89" s="2">
-        <v>46027.50440972222</v>
+        <v>46027.67233796296</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G89" s="2">
-        <v>19.35</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G89" s="2"/>
       <c r="H89" s="2">
         <v>0</v>
       </c>
@@ -3967,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -3975,23 +3848,21 @@
         <v>83</v>
       </c>
       <c r="B90" s="2">
-        <v>46027.32740740741</v>
+        <v>46027.31991898148</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D90" s="2">
-        <v>46027.69796296296</v>
+        <v>46027.67479166666</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G90" s="2">
-        <v>23</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G90" s="2"/>
       <c r="H90" s="2">
         <v>0</v>
       </c>
@@ -3999,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -4007,31 +3878,31 @@
         <v>84</v>
       </c>
       <c r="B91" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.33503472222</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D91" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.66853009259</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G91" s="2">
-        <v>20.95</v>
+        <v>18.6</v>
       </c>
       <c r="H91" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I91" s="2">
         <v>0</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -4039,31 +3910,29 @@
         <v>85</v>
       </c>
       <c r="B92" s="2">
-        <v>46027.32732638889</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D92" s="2">
-        <v>46027.68935185186</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G92" s="2">
-        <v>23.35</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="G92" s="2"/>
       <c r="H92" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I92" s="2">
         <v>0</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -4074,20 +3943,18 @@
         <v>46027.31789351852</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D93" s="2">
         <v>46027.47284722222</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G93" s="2">
-        <v>22.4</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="G93" s="2"/>
       <c r="H93" s="2">
         <v>0</v>
       </c>
@@ -4095,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -4103,23 +3970,21 @@
         <v>87</v>
       </c>
       <c r="B94" s="2">
-        <v>46027.31099537037</v>
+        <v>46027.31944444445</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D94" s="2">
-        <v>46027.73664351852</v>
+        <v>46027.68828703704</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G94" s="2">
-        <v>18.35</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="G94" s="2"/>
       <c r="H94" s="2">
         <v>0</v>
       </c>
@@ -4127,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -4135,23 +4000,21 @@
         <v>88</v>
       </c>
       <c r="B95" s="2">
-        <v>46027.51956018519</v>
+        <v>46027.32732638889</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D95" s="2">
-        <v>46027.73401620371</v>
+        <v>46027.68935185186</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G95" s="2">
-        <v>18.35</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="G95" s="2"/>
       <c r="H95" s="2">
         <v>0</v>
       </c>
@@ -4159,31 +4022,29 @@
         <v>0</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B96" s="2">
-        <v>46027.31196759259</v>
+        <v>46027.32740740741</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D96" s="2">
-        <v>46027.50578703704</v>
+        <v>46027.69796296296</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G96" s="2">
-        <v>18.35</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="G96" s="2"/>
       <c r="H96" s="2">
         <v>0</v>
       </c>
@@ -4191,31 +4052,29 @@
         <v>0</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B97" s="2">
-        <v>46027.57388888889</v>
+        <v>46027.50734953704</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D97" s="2">
-        <v>46027.73664351852</v>
+        <v>46027.73299768518</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G97" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G97" s="2"/>
       <c r="H97" s="2">
         <v>0</v>
       </c>
@@ -4223,31 +4082,29 @@
         <v>0</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B98" s="2">
         <v>46027.6</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D98" s="2">
         <v>46027.73295138889</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G98" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G98" s="2"/>
       <c r="H98" s="2">
         <v>0</v>
       </c>
@@ -4255,31 +4112,29 @@
         <v>0</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B99" s="2">
-        <v>46027.62979166667</v>
+        <v>46027.57628472222</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D99" s="2">
-        <v>46027.73474537037</v>
+        <v>46027.73366898148</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G99" s="2">
-        <v>23</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G99" s="2"/>
       <c r="H99" s="2">
         <v>0</v>
       </c>
@@ -4287,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -4295,23 +4150,21 @@
         <v>91</v>
       </c>
       <c r="B100" s="2">
-        <v>46027.30591435185</v>
+        <v>46027.30096064815</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D100" s="2">
-        <v>46027.5315625</v>
+        <v>46027.58107638889</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G100" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G100" s="2"/>
       <c r="H100" s="2">
         <v>0</v>
       </c>
@@ -4319,31 +4172,29 @@
         <v>0</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B101" s="2">
-        <v>46027.54512731481</v>
+        <v>46027.30211805556</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D101" s="2">
-        <v>46027.73289351852</v>
+        <v>46027.5430324074</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G101" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G101" s="2"/>
       <c r="H101" s="2">
         <v>0</v>
       </c>
@@ -4351,31 +4202,29 @@
         <v>0</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B102" s="2">
-        <v>46027.30096064815</v>
+        <v>46027.54512731481</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D102" s="2">
-        <v>46027.58107638889</v>
+        <v>46027.73289351852</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G102" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G102" s="2"/>
       <c r="H102" s="2">
         <v>0</v>
       </c>
@@ -4383,31 +4232,29 @@
         <v>0</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B103" s="2">
-        <v>46027.30172453704</v>
+        <v>46027.30591435185</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D103" s="2">
-        <v>46027.73307870371</v>
+        <v>46027.5315625</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G103" s="2">
-        <v>19.25</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G103" s="2"/>
       <c r="H103" s="2">
         <v>0</v>
       </c>
@@ -4415,31 +4262,29 @@
         <v>0</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B104" s="2">
-        <v>46027.33629629629</v>
+        <v>46027.30262731481</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D104" s="2">
-        <v>46027.608125</v>
+        <v>46027.73355324074</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G104" s="2">
-        <v>23</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G104" s="2"/>
       <c r="H104" s="2">
         <v>0</v>
       </c>
@@ -4447,31 +4292,29 @@
         <v>0</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B105" s="2">
-        <v>46027.30045138889</v>
+        <v>46027.31196759259</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D105" s="2">
-        <v>46027.53990740741</v>
+        <v>46027.50578703704</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G105" s="2">
-        <v>18.6</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G105" s="2"/>
       <c r="H105" s="2">
         <v>0</v>
       </c>
@@ -4479,31 +4322,29 @@
         <v>0</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B106" s="2">
-        <v>46027.30118055556</v>
+        <v>46027.51956018519</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D106" s="2">
-        <v>46027.73304398148</v>
+        <v>46027.73401620371</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G106" s="2">
-        <v>18.6</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G106" s="2"/>
       <c r="H106" s="2">
         <v>0</v>
       </c>
@@ -4511,31 +4352,29 @@
         <v>0</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B107" s="2">
-        <v>46027.30252314815</v>
+        <v>46027.31099537037</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D107" s="2">
-        <v>46027.48818287037</v>
+        <v>46027.52083333334</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G107" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G107" s="2"/>
       <c r="H107" s="2">
         <v>0</v>
       </c>
@@ -4543,31 +4382,29 @@
         <v>0</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B108" s="2">
-        <v>46027.30262731481</v>
+        <v>46027.57388888889</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D108" s="2">
-        <v>46027.73355324074</v>
+        <v>46027.73664351852</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G108" s="2">
-        <v>19.75</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G108" s="2"/>
       <c r="H108" s="2">
         <v>0</v>
       </c>
@@ -4575,31 +4412,29 @@
         <v>0</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B109" s="2">
-        <v>46027.30211805556</v>
+        <v>46027.33629629629</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D109" s="2">
-        <v>46027.5430324074</v>
+        <v>46027.608125</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G109" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G109" s="2"/>
       <c r="H109" s="2">
         <v>0</v>
       </c>
@@ -4607,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -4615,23 +4450,21 @@
         <v>98</v>
       </c>
       <c r="B110" s="2">
-        <v>46027.57628472222</v>
+        <v>46027.62979166667</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D110" s="2">
-        <v>46027.73366898148</v>
+        <v>46027.73474537037</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G110" s="2">
-        <v>20.7</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G110" s="2"/>
       <c r="H110" s="2">
         <v>0</v>
       </c>
@@ -4639,31 +4472,29 @@
         <v>0</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B111" s="2">
-        <v>46027.30180555556</v>
+        <v>46027.30252314815</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D111" s="2">
-        <v>46027.55563657408</v>
+        <v>46027.48818287037</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G111" s="2">
-        <v>20.7</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G111" s="2"/>
       <c r="H111" s="2">
         <v>0</v>
       </c>
@@ -4671,31 +4502,29 @@
         <v>0</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B112" s="2">
-        <v>46027.55086805556</v>
+        <v>46027.30180555556</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D112" s="2">
-        <v>46027.73302083334</v>
+        <v>46027.55563657408</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G112" s="2">
-        <v>18.6</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G112" s="2"/>
       <c r="H112" s="2">
         <v>0</v>
       </c>
@@ -4703,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -4711,19 +4540,21 @@
         <v>99</v>
       </c>
       <c r="B113" s="2">
-        <v>46027.30270833334</v>
+        <v>46027.31141203704</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D113" s="2">
+        <v>46027.50634259259</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F113" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G113" s="2">
-        <v>19.25</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G113" s="2"/>
       <c r="H113" s="2">
         <v>0</v>
       </c>
@@ -4731,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -4739,23 +4570,21 @@
         <v>100</v>
       </c>
       <c r="B114" s="2">
-        <v>46027.31141203704</v>
+        <v>46027.30172453704</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D114" s="2">
-        <v>46027.50634259259</v>
+        <v>46027.73307870371</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G114" s="2">
-        <v>18.6</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G114" s="2"/>
       <c r="H114" s="2">
         <v>0</v>
       </c>
@@ -4763,31 +4592,29 @@
         <v>0</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B115" s="2">
-        <v>46027.50734953704</v>
+        <v>46027.30045138889</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D115" s="2">
-        <v>46027.73299768518</v>
+        <v>46027.53990740741</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G115" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G115" s="2"/>
       <c r="H115" s="2">
         <v>0</v>
       </c>
@@ -4795,31 +4622,29 @@
         <v>0</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B116" s="2">
-        <v>46027.51991898148</v>
+        <v>46027.55086805556</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D116" s="2">
-        <v>46027.73395833333</v>
+        <v>46027.73302083334</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G116" s="2">
-        <v>18.6</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G116" s="2"/>
       <c r="H116" s="2">
         <v>0</v>
       </c>
@@ -4827,31 +4652,29 @@
         <v>0</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B117" s="2">
-        <v>46027.33277777778</v>
+        <v>46027.30270833334</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D117" s="2">
-        <v>46027.6758449074</v>
+        <v>46027.63541666666</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G117" s="2">
-        <v>19.75</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G117" s="2"/>
       <c r="H117" s="2">
         <v>0</v>
       </c>
@@ -4859,31 +4682,29 @@
         <v>0</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B118" s="2">
-        <v>46027.3353125</v>
+        <v>46027.30118055556</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D118" s="2">
-        <v>46027.57923611111</v>
+        <v>46027.73304398148</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G118" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G118" s="2"/>
       <c r="H118" s="2">
         <v>0</v>
       </c>
@@ -4891,31 +4712,29 @@
         <v>0</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B119" s="2">
-        <v>46027.5837962963</v>
+        <v>46027.51991898148</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D119" s="2">
-        <v>46027.7166087963</v>
+        <v>46027.73395833333</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G119" s="2">
-        <v>18.35</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="G119" s="2"/>
       <c r="H119" s="2">
         <v>0</v>
       </c>
@@ -4923,31 +4742,29 @@
         <v>0</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B120" s="2">
-        <v>46027.33101851852</v>
+        <v>46027.33277777778</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D120" s="2">
-        <v>46027.60766203704</v>
+        <v>46027.6758449074</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G120" s="2">
-        <v>18.35</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="G120" s="2"/>
       <c r="H120" s="2">
         <v>0</v>
       </c>
@@ -4955,31 +4772,29 @@
         <v>0</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B121" s="2">
-        <v>46027.5822337963</v>
+        <v>46027.3353125</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D121" s="2">
-        <v>46027.71527777778</v>
+        <v>46027.57923611111</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G121" s="2">
-        <v>23</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="G121" s="2"/>
       <c r="H121" s="2">
         <v>0</v>
       </c>
@@ -4987,31 +4802,29 @@
         <v>0</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B122" s="2">
-        <v>46027.32804398148</v>
+        <v>46027.5837962963</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D122" s="2">
-        <v>46027.55920138889</v>
+        <v>46027.7166087963</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G122" s="2">
-        <v>23</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="G122" s="2"/>
       <c r="H122" s="2">
         <v>0</v>
       </c>
@@ -5019,31 +4832,29 @@
         <v>0</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B123" s="2">
-        <v>46027.37483796296</v>
+        <v>46027.32804398148</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D123" s="2">
-        <v>46027.7074074074</v>
+        <v>46027.55920138889</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G123" s="2">
-        <v>18.35</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G123" s="2"/>
       <c r="H123" s="2">
         <v>0</v>
       </c>
@@ -5051,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -5059,23 +4870,21 @@
         <v>106</v>
       </c>
       <c r="B124" s="2">
-        <v>46027.62797453703</v>
+        <v>46027.5822337963</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D124" s="2">
-        <v>46027.69224537037</v>
+        <v>46027.71527777778</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G124" s="2">
-        <v>19.25</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G124" s="2"/>
       <c r="H124" s="2">
         <v>0</v>
       </c>
@@ -5083,31 +4892,29 @@
         <v>0</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B125" s="2">
-        <v>46027.35962962963</v>
+        <v>46027.33101851852</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D125" s="2">
-        <v>46027.61256944444</v>
+        <v>46027.60766203704</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G125" s="2">
-        <v>19.25</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G125" s="2"/>
       <c r="H125" s="2">
         <v>0</v>
       </c>
@@ -5115,31 +4922,29 @@
         <v>0</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B126" s="2">
-        <v>46027.36927083333</v>
+        <v>46027.62797453703</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D126" s="2">
-        <v>46027.75387731481</v>
+        <v>46027.69224537037</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G126" s="2">
-        <v>18.35</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="G126" s="2"/>
       <c r="H126" s="2">
         <v>0</v>
       </c>
@@ -5147,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -5155,23 +4960,21 @@
         <v>108</v>
       </c>
       <c r="B127" s="2">
-        <v>46027.47921296296</v>
+        <v>46027.35962962963</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D127" s="2">
-        <v>46027.71436342593</v>
+        <v>46027.61256944444</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G127" s="2">
-        <v>18.35</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="G127" s="2"/>
       <c r="H127" s="2">
         <v>0</v>
       </c>
@@ -5179,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -5187,23 +4990,21 @@
         <v>109</v>
       </c>
       <c r="B128" s="2">
-        <v>46027.35225694445</v>
+        <v>46027.37483796296</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D128" s="2">
-        <v>46027.67958333333</v>
+        <v>46027.7074074074</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G128" s="2">
-        <v>18.35</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="G128" s="2"/>
       <c r="H128" s="2">
         <v>0</v>
       </c>
@@ -5211,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -5219,23 +5020,21 @@
         <v>110</v>
       </c>
       <c r="B129" s="2">
-        <v>46027.46614583334</v>
+        <v>46027.33344907407</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D129" s="2">
-        <v>46027.67943287037</v>
+        <v>46027.68206018519</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G129" s="2">
-        <v>18.35</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G129" s="2"/>
       <c r="H129" s="2">
         <v>0</v>
       </c>
@@ -5243,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -5251,23 +5050,21 @@
         <v>111</v>
       </c>
       <c r="B130" s="2">
-        <v>46027.45618055556</v>
+        <v>46027.46614583334</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D130" s="2">
-        <v>46027.67900462963</v>
+        <v>46027.67943287037</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G130" s="2">
-        <v>18.35</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G130" s="2"/>
       <c r="H130" s="2">
         <v>0</v>
       </c>
@@ -5275,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -5283,19 +5080,19 @@
         <v>112</v>
       </c>
       <c r="B131" s="2">
-        <v>46027.37284722222</v>
+        <v>46027</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D131" s="2">
-        <v>46027.72733796296</v>
+        <v>46027</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G131" s="2">
         <v>15.9</v>
@@ -5304,33 +5101,33 @@
         <v>0</v>
       </c>
       <c r="I131" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B132" s="2">
-        <v>46027.31988425926</v>
+        <v>46027.37284722222</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D132" s="2">
-        <v>46027.62060185185</v>
+        <v>46027.72733796296</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G132" s="2">
-        <v>18.7</v>
+        <v>15.9</v>
       </c>
       <c r="H132" s="2">
         <v>0</v>
@@ -5339,63 +5136,59 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B133" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.31988425926</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D133" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.62060185185</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G133" s="2">
-        <v>18.35</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G133" s="2"/>
       <c r="H133" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I133" s="2">
         <v>0</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B134" s="2">
-        <v>46027.33344907407</v>
+        <v>46027.45618055556</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D134" s="2">
-        <v>46027.68206018519</v>
+        <v>46027.67900462963</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G134" s="2">
-        <v>22.4</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G134" s="2"/>
       <c r="H134" s="2">
         <v>0</v>
       </c>
@@ -5403,39 +5196,37 @@
         <v>0</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B135" s="2">
-        <v>46027</v>
+        <v>46027.36927083333</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D135" s="2">
-        <v>46027</v>
+        <v>46027.75387731481</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G135" s="2">
-        <v>15.9</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G135" s="2"/>
       <c r="H135" s="2">
         <v>0</v>
       </c>
       <c r="I135" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -5446,20 +5237,18 @@
         <v>46027.33333333334</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D136" s="2">
         <v>46027.33333333334</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G136" s="2">
-        <v>18.7</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G136" s="2"/>
       <c r="H136" s="2">
         <v>8</v>
       </c>
@@ -5467,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -5475,23 +5264,21 @@
         <v>117</v>
       </c>
       <c r="B137" s="2">
-        <v>46027.31133101852</v>
+        <v>46027.47921296296</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D137" s="2">
-        <v>46027.60391203704</v>
+        <v>46027.71436342593</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G137" s="2">
-        <v>18.35</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G137" s="2"/>
       <c r="H137" s="2">
         <v>0</v>
       </c>
@@ -5499,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -5507,23 +5294,21 @@
         <v>118</v>
       </c>
       <c r="B138" s="2">
-        <v>46027.29341435185</v>
+        <v>46027.35225694445</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D138" s="2">
-        <v>46027.69791666666</v>
+        <v>46027.67958333333</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G138" s="2">
-        <v>18.35</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="G138" s="2"/>
       <c r="H138" s="2">
         <v>0</v>
       </c>
@@ -5531,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -5539,31 +5324,31 @@
         <v>119</v>
       </c>
       <c r="B139" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.45893518518</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D139" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.71310185185</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G139" s="2">
         <v>18.35</v>
       </c>
       <c r="H139" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I139" s="2">
         <v>0</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -5571,23 +5356,21 @@
         <v>120</v>
       </c>
       <c r="B140" s="2">
-        <v>46027.38177083333</v>
+        <v>46027.36002314815</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D140" s="2">
-        <v>46027.66678240741</v>
+        <v>46027.73366898148</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G140" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G140" s="2"/>
       <c r="H140" s="2">
         <v>0</v>
       </c>
@@ -5595,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -5603,23 +5386,21 @@
         <v>121</v>
       </c>
       <c r="B141" s="2">
-        <v>46027.43018518519</v>
+        <v>46027.45662037037</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D141" s="2">
-        <v>46027.73777777778</v>
+        <v>46027.71114583333</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G141" s="2">
-        <v>20.2</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G141" s="2"/>
       <c r="H141" s="2">
         <v>0</v>
       </c>
@@ -5627,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -5635,31 +5416,29 @@
         <v>122</v>
       </c>
       <c r="B142" s="2">
-        <v>46027.45662037037</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D142" s="2">
-        <v>46027.71114583333</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G142" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G142" s="2"/>
       <c r="H142" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I142" s="2">
         <v>0</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -5667,23 +5446,21 @@
         <v>123</v>
       </c>
       <c r="B143" s="2">
-        <v>46027.45625</v>
+        <v>46027.30584490741</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D143" s="2">
-        <v>46027.71776620371</v>
+        <v>46027.70478009259</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G143" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G143" s="2"/>
       <c r="H143" s="2">
         <v>0</v>
       </c>
@@ -5691,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -5699,23 +5476,21 @@
         <v>124</v>
       </c>
       <c r="B144" s="2">
-        <v>46027.28606481481</v>
+        <v>46027.30576388889</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D144" s="2">
-        <v>46027.59731481481</v>
+        <v>46027.62216435185</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G144" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G144" s="2"/>
       <c r="H144" s="2">
         <v>0</v>
       </c>
@@ -5723,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -5731,23 +5506,21 @@
         <v>125</v>
       </c>
       <c r="B145" s="2">
-        <v>46027.36002314815</v>
+        <v>46027.41646990741</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D145" s="2">
-        <v>46027.73366898148</v>
+        <v>46027.64012731481</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G145" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G145" s="2"/>
       <c r="H145" s="2">
         <v>0</v>
       </c>
@@ -5755,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -5763,31 +5536,29 @@
         <v>126</v>
       </c>
       <c r="B146" s="2">
-        <v>46027.30576388889</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D146" s="2">
-        <v>46027.62216435185</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G146" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G146" s="2"/>
       <c r="H146" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I146" s="2">
         <v>0</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -5795,23 +5566,21 @@
         <v>127</v>
       </c>
       <c r="B147" s="2">
-        <v>46027.28559027778</v>
+        <v>46027.38177083333</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D147" s="2">
-        <v>46027.59752314815</v>
+        <v>46027.66678240741</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G147" s="2">
-        <v>20.2</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G147" s="2"/>
       <c r="H147" s="2">
         <v>0</v>
       </c>
@@ -5819,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -5830,20 +5599,18 @@
         <v>46027.33333333334</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D148" s="2">
         <v>46027.33333333334</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G148" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G148" s="2"/>
       <c r="H148" s="2">
         <v>8</v>
       </c>
@@ -5851,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -5859,23 +5626,21 @@
         <v>129</v>
       </c>
       <c r="B149" s="2">
-        <v>46027.45893518518</v>
+        <v>46027.28559027778</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D149" s="2">
-        <v>46027.71310185185</v>
+        <v>46027.59752314815</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G149" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G149" s="2"/>
       <c r="H149" s="2">
         <v>0</v>
       </c>
@@ -5883,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -5891,31 +5656,29 @@
         <v>130</v>
       </c>
       <c r="B150" s="2">
-        <v>46027.9411574074</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D150" s="2">
-        <v>46027.94627314815</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G150" s="2">
-        <v>23.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G150" s="2"/>
       <c r="H150" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I150" s="2">
         <v>0</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -5923,31 +5686,29 @@
         <v>131</v>
       </c>
       <c r="B151" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.9411574074</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D151" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.94627314815</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G151" s="2">
-        <v>18.7</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G151" s="2"/>
       <c r="H151" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I151" s="2">
         <v>0</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -5955,23 +5716,21 @@
         <v>132</v>
       </c>
       <c r="B152" s="2">
-        <v>46027.41646990741</v>
+        <v>46027.29341435185</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D152" s="2">
-        <v>46027.64012731481</v>
+        <v>46027.69791666666</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G152" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G152" s="2"/>
       <c r="H152" s="2">
         <v>0</v>
       </c>
@@ -5979,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -5987,23 +5746,21 @@
         <v>133</v>
       </c>
       <c r="B153" s="2">
-        <v>46027.30158564815</v>
+        <v>46027.43018518519</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D153" s="2">
-        <v>46027.62318287037</v>
+        <v>46027.73777777778</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G153" s="2">
-        <v>18.7</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G153" s="2"/>
       <c r="H153" s="2">
         <v>0</v>
       </c>
@@ -6011,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -6019,23 +5776,21 @@
         <v>134</v>
       </c>
       <c r="B154" s="2">
-        <v>46027.30259259259</v>
+        <v>46027.37342592593</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D154" s="2">
-        <v>46027.60326388889</v>
+        <v>46027.62313657408</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G154" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G154" s="2"/>
       <c r="H154" s="2">
         <v>0</v>
       </c>
@@ -6043,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -6051,22 +5806,22 @@
         <v>135</v>
       </c>
       <c r="B155" s="2">
-        <v>46027.37342592593</v>
+        <v>46027.48381944445</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D155" s="2">
-        <v>46027.62313657408</v>
+        <v>46027.7019212963</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G155" s="2">
-        <v>18.35</v>
+        <v>19.65</v>
       </c>
       <c r="H155" s="2">
         <v>0</v>
@@ -6075,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -6083,23 +5838,21 @@
         <v>136</v>
       </c>
       <c r="B156" s="2">
-        <v>46027.48381944445</v>
+        <v>46027.28606481481</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D156" s="2">
-        <v>46027.7019212963</v>
+        <v>46027.59731481481</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G156" s="2">
-        <v>19.65</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G156" s="2"/>
       <c r="H156" s="2">
         <v>0</v>
       </c>
@@ -6107,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -6115,31 +5868,29 @@
         <v>137</v>
       </c>
       <c r="B157" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.30259259259</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D157" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.60326388889</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G157" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G157" s="2"/>
       <c r="H157" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I157" s="2">
         <v>0</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -6147,23 +5898,21 @@
         <v>138</v>
       </c>
       <c r="B158" s="2">
-        <v>46027.30584490741</v>
+        <v>46027.30158564815</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D158" s="2">
-        <v>46027.70478009259</v>
+        <v>46027.62318287037</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G158" s="2">
-        <v>23.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G158" s="2"/>
       <c r="H158" s="2">
         <v>0</v>
       </c>
@@ -6171,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -6179,23 +5928,21 @@
         <v>139</v>
       </c>
       <c r="B159" s="2">
-        <v>46027.57763888889</v>
+        <v>46027.31133101852</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D159" s="2">
-        <v>46027.8869212963</v>
+        <v>46027.60391203704</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G159" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G159" s="2"/>
       <c r="H159" s="2">
         <v>0</v>
       </c>
@@ -6203,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -6211,23 +5958,21 @@
         <v>140</v>
       </c>
       <c r="B160" s="2">
-        <v>46027.56222222222</v>
+        <v>46027.45625</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D160" s="2">
-        <v>46027.88688657407</v>
+        <v>46027.71776620371</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G160" s="2">
-        <v>19.25</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G160" s="2"/>
       <c r="H160" s="2">
         <v>0</v>
       </c>
@@ -6235,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -6243,31 +5988,29 @@
         <v>141</v>
       </c>
       <c r="B161" s="2">
-        <v>46027.4537037037</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D161" s="2">
-        <v>46027.61899305556</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G161" s="2">
-        <v>18.35</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G161" s="2"/>
       <c r="H161" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I161" s="2">
         <v>0</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -6275,19 +6018,21 @@
         <v>142</v>
       </c>
       <c r="B162" s="2">
-        <v>46027.69326388889</v>
+        <v>46027.56222222222</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D162" s="2">
+        <v>46027.88688657407</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F162" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G162" s="2">
-        <v>20.7</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="G162" s="2"/>
       <c r="H162" s="2">
         <v>0</v>
       </c>
@@ -6295,31 +6040,29 @@
         <v>0</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B163" s="2">
-        <v>46027.37841435185</v>
+        <v>46027.57763888889</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D163" s="2">
-        <v>46027.69324074074</v>
+        <v>46027.8869212963</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G163" s="2">
-        <v>20.7</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="G163" s="2"/>
       <c r="H163" s="2">
         <v>0</v>
       </c>
@@ -6327,31 +6070,29 @@
         <v>0</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="164" spans="1:10">
       <c r="A164" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B164" s="2">
-        <v>46027.37293981481</v>
+        <v>46027.37234953704</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D164" s="2">
-        <v>46027.63403935185</v>
+        <v>46027.6875</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G164" s="2">
-        <v>23.35</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G164" s="2"/>
       <c r="H164" s="2">
         <v>0</v>
       </c>
@@ -6359,31 +6100,29 @@
         <v>0</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B165" s="2">
-        <v>46027.37234953704</v>
+        <v>46027.4537037037</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D165" s="2">
-        <v>46027.6875</v>
+        <v>46027.61899305556</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G165" s="2">
-        <v>18.7</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G165" s="2"/>
       <c r="H165" s="2">
         <v>0</v>
       </c>
@@ -6391,31 +6130,29 @@
         <v>0</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="166" spans="1:10">
       <c r="A166" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B166" s="2">
-        <v>46027.37340277778</v>
+        <v>46027.41046296297</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D166" s="2">
-        <v>46027.68671296296</v>
+        <v>46027.67003472222</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G166" s="2">
-        <v>18.35</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G166" s="2"/>
       <c r="H166" s="2">
         <v>0</v>
       </c>
@@ -6423,31 +6160,29 @@
         <v>0</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="167" spans="1:10">
       <c r="A167" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B167" s="2">
-        <v>46027.41046296297</v>
+        <v>46027.37340277778</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D167" s="2">
-        <v>46027.67003472222</v>
+        <v>46027.68671296296</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G167" s="2">
-        <v>18.35</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G167" s="2"/>
       <c r="H167" s="2">
         <v>0</v>
       </c>
@@ -6455,27 +6190,29 @@
         <v>0</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B168" s="2">
-        <v>46027.98270833334</v>
+        <v>46027.37293981481</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D168" s="2">
+        <v>46027.63403935185</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F168" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G168" s="2">
-        <v>19.65</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G168" s="2"/>
       <c r="H168" s="2">
         <v>0</v>
       </c>
@@ -6483,31 +6220,29 @@
         <v>0</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="169" spans="1:10">
       <c r="A169" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B169" s="2">
-        <v>46027.27115740741</v>
+        <v>46027.37841435185</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D169" s="2">
-        <v>46027.5049537037</v>
+        <v>46027.69324074074</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G169" s="2">
-        <v>19.25</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G169" s="2"/>
       <c r="H169" s="2">
         <v>0</v>
       </c>
@@ -6515,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -6523,23 +6258,17 @@
         <v>149</v>
       </c>
       <c r="B170" s="2">
-        <v>46027.60428240741</v>
+        <v>46027.69326388889</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D170" s="2">
-        <v>46027.87864583333</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>192</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
       <c r="F170" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G170" s="2">
-        <v>25.7</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G170" s="2"/>
       <c r="H170" s="2">
         <v>0</v>
       </c>
@@ -6547,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -6555,23 +6284,21 @@
         <v>150</v>
       </c>
       <c r="B171" s="2">
-        <v>46027.54149305556</v>
+        <v>46027.60428240741</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D171" s="2">
-        <v>46027.6778125</v>
+        <v>46027.87864583333</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G171" s="2">
-        <v>23</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="G171" s="2"/>
       <c r="H171" s="2">
         <v>0</v>
       </c>
@@ -6579,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -6587,22 +6314,22 @@
         <v>151</v>
       </c>
       <c r="B172" s="2">
-        <v>46027.37047453703</v>
+        <v>46027.98270833334</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D172" s="2">
-        <v>46027.65521990741</v>
+        <v>46028.26078703703</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G172" s="2">
-        <v>20.2</v>
+        <v>19.65</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
@@ -6611,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -6619,23 +6346,21 @@
         <v>152</v>
       </c>
       <c r="B173" s="2">
-        <v>46027.33436342593</v>
+        <v>46027.27115740741</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D173" s="2">
-        <v>46027.50951388889</v>
+        <v>46027.5049537037</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G173" s="2">
-        <v>20.7</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="G173" s="2"/>
       <c r="H173" s="2">
         <v>0</v>
       </c>
@@ -6643,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -6651,23 +6376,21 @@
         <v>153</v>
       </c>
       <c r="B174" s="2">
-        <v>46027.38131944444</v>
+        <v>46027.37047453703</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D174" s="2">
-        <v>46027.59186342593</v>
+        <v>46027.65521990741</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G174" s="2">
-        <v>20.2</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G174" s="2"/>
       <c r="H174" s="2">
         <v>0</v>
       </c>
@@ -6675,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -6683,23 +6406,21 @@
         <v>154</v>
       </c>
       <c r="B175" s="2">
-        <v>46027.3749537037</v>
+        <v>46027.54149305556</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D175" s="2">
-        <v>46027.59524305556</v>
+        <v>46027.6778125</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G175" s="2">
-        <v>20.2</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G175" s="2"/>
       <c r="H175" s="2">
         <v>0</v>
       </c>
@@ -6707,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -6715,31 +6436,29 @@
         <v>155</v>
       </c>
       <c r="B176" s="2">
-        <v>46027.5</v>
+        <v>46027.33436342593</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D176" s="2">
-        <v>46027.5</v>
+        <v>46027.50951388889</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G176" s="2">
-        <v>19.6</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G176" s="2"/>
       <c r="H176" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I176" s="2">
         <v>0</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -6747,19 +6466,21 @@
         <v>156</v>
       </c>
       <c r="B177" s="2">
-        <v>46027.32055555555</v>
+        <v>46027.3749537037</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D177" s="2"/>
-      <c r="E177" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D177" s="2">
+        <v>46027.59524305556</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F177" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G177" s="2">
-        <v>19.6</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G177" s="2"/>
       <c r="H177" s="2">
         <v>0</v>
       </c>
@@ -6767,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -6775,23 +6496,21 @@
         <v>157</v>
       </c>
       <c r="B178" s="2">
-        <v>46027.34502314815</v>
+        <v>46027.38131944444</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D178" s="2">
-        <v>46027.4375</v>
+        <v>46027.59186342593</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G178" s="2">
-        <v>19.25</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G178" s="2"/>
       <c r="H178" s="2">
         <v>0</v>
       </c>
@@ -6799,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -6807,31 +6526,29 @@
         <v>158</v>
       </c>
       <c r="B179" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.34502314815</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D179" s="2">
-        <v>46027.33333333334</v>
+        <v>46027.4375</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G179" s="2">
-        <v>19.25</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G179" s="2"/>
       <c r="H179" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I179" s="2">
         <v>0</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -6842,20 +6559,18 @@
         <v>46027.35664351852</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D180" s="2">
         <v>46027.50685185185</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G180" s="2">
-        <v>19.25</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G180" s="2"/>
       <c r="H180" s="2">
         <v>0</v>
       </c>
@@ -6863,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -6871,31 +6586,29 @@
         <v>160</v>
       </c>
       <c r="B181" s="2">
-        <v>46027.40987268519</v>
+        <v>46027.5</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D181" s="2">
-        <v>46027.67278935185</v>
+        <v>46027.5</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G181" s="2">
-        <v>23.85</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G181" s="2"/>
       <c r="H181" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I181" s="2">
         <v>0</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -6903,31 +6616,29 @@
         <v>161</v>
       </c>
       <c r="B182" s="2">
-        <v>46027.33827546296</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D182" s="2">
-        <v>46027.5584837963</v>
+        <v>46027.33333333334</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G182" s="2">
-        <v>19.6</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G182" s="2"/>
       <c r="H182" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I182" s="2">
         <v>0</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -6935,23 +6646,21 @@
         <v>162</v>
       </c>
       <c r="B183" s="2">
-        <v>46027.34408564815</v>
+        <v>46027.40987268519</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D183" s="2">
-        <v>46027.51533564815</v>
+        <v>46027.67278935185</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G183" s="2">
-        <v>19.75</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G183" s="2"/>
       <c r="H183" s="2">
         <v>0</v>
       </c>
@@ -6959,7 +6668,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -6967,23 +6676,21 @@
         <v>163</v>
       </c>
       <c r="B184" s="2">
-        <v>46027.33337962963</v>
+        <v>46027.34408564815</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D184" s="2">
-        <v>46027.51506944445</v>
+        <v>46027.51533564815</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G184" s="2">
-        <v>22.4</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G184" s="2"/>
       <c r="H184" s="2">
         <v>0</v>
       </c>
@@ -6991,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -6999,23 +6706,21 @@
         <v>164</v>
       </c>
       <c r="B185" s="2">
-        <v>46027.31473379629</v>
+        <v>46027.33827546296</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D185" s="2">
-        <v>46027.77425925926</v>
+        <v>46027.5584837963</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G185" s="2">
-        <v>22.4</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G185" s="2"/>
       <c r="H185" s="2">
         <v>0</v>
       </c>
@@ -7023,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -7031,23 +6736,17 @@
         <v>165</v>
       </c>
       <c r="B186" s="2">
-        <v>46027.31033564815</v>
+        <v>46027.32055555555</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D186" s="2">
-        <v>46027.63726851852</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>192</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
       <c r="F186" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G186" s="2">
-        <v>22.4</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G186" s="2"/>
       <c r="H186" s="2">
         <v>0</v>
       </c>
@@ -7055,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -7063,23 +6762,21 @@
         <v>166</v>
       </c>
       <c r="B187" s="2">
-        <v>46027.61831018519</v>
+        <v>46027.31473379629</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D187" s="2">
-        <v>46027.68756944445</v>
+        <v>46027.77425925926</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G187" s="2">
-        <v>20.7</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="G187" s="2"/>
       <c r="H187" s="2">
         <v>0</v>
       </c>
@@ -7087,7 +6784,7 @@
         <v>0</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -7095,23 +6792,21 @@
         <v>167</v>
       </c>
       <c r="B188" s="2">
-        <v>46027.5225</v>
+        <v>46027.31033564815</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D188" s="2">
-        <v>46027.8546875</v>
+        <v>46027.63726851852</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G188" s="2">
-        <v>24.8</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="G188" s="2"/>
       <c r="H188" s="2">
         <v>0</v>
       </c>
@@ -7119,31 +6814,29 @@
         <v>0</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="189" spans="1:10">
       <c r="A189" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B189" s="2">
-        <v>46027.38115740741</v>
+        <v>46027.33337962963</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D189" s="2">
-        <v>46027.50145833333</v>
+        <v>46027.51506944445</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G189" s="2">
-        <v>24.8</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="G189" s="2"/>
       <c r="H189" s="2">
         <v>0</v>
       </c>
@@ -7151,31 +6844,29 @@
         <v>0</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="190" spans="1:10">
       <c r="A190" s="2" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B190" s="2">
-        <v>46027.53438657407</v>
+        <v>46027.33511574074</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D190" s="2">
-        <v>46027.68799768519</v>
+        <v>46027.56357638889</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G190" s="2">
-        <v>20.7</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G190" s="2"/>
       <c r="H190" s="2">
         <v>0</v>
       </c>
@@ -7183,31 +6874,29 @@
         <v>0</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="191" spans="1:10">
       <c r="A191" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B191" s="2">
         <v>46027.70170138889</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D191" s="2">
         <v>46027.985</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G191" s="2">
-        <v>20.7</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G191" s="2"/>
       <c r="H191" s="2">
         <v>0</v>
       </c>
@@ -7215,31 +6904,29 @@
         <v>0</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B192" s="2">
-        <v>46027.33511574074</v>
+        <v>46027.5225</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D192" s="2">
-        <v>46027.56357638889</v>
+        <v>46027.8546875</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G192" s="2">
-        <v>20.7</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G192" s="2"/>
       <c r="H192" s="2">
         <v>0</v>
       </c>
@@ -7247,30 +6934,30 @@
         <v>0</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="193" spans="1:10">
       <c r="A193" s="2" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="B193" s="2">
-        <v>46027.67787037037</v>
+        <v>46027.70638888889</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D193" s="2">
-        <v>46027.98534722222</v>
+        <v>46028.3159837963</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G193" s="2">
-        <v>23</v>
+        <v>19.65</v>
       </c>
       <c r="H193" s="2">
         <v>0</v>
@@ -7279,31 +6966,29 @@
         <v>0</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="194" spans="1:10">
       <c r="A194" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B194" s="2">
-        <v>46027.33265046297</v>
+        <v>46027.67787037037</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D194" s="2">
-        <v>46027.59347222222</v>
+        <v>46027.98534722222</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G194" s="2">
-        <v>20.7</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G194" s="2"/>
       <c r="H194" s="2">
         <v>0</v>
       </c>
@@ -7311,31 +6996,29 @@
         <v>0</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="195" spans="1:10">
       <c r="A195" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B195" s="2">
-        <v>46027.5818287037</v>
+        <v>46027.38115740741</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D195" s="2">
-        <v>46027.68847222222</v>
+        <v>46027.50145833333</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G195" s="2">
-        <v>20.7</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G195" s="2"/>
       <c r="H195" s="2">
         <v>0</v>
       </c>
@@ -7343,27 +7026,27 @@
         <v>0</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="196" spans="1:10">
       <c r="A196" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B196" s="2">
         <v>46027.68622685185</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D196" s="2">
         <v>46027.98535879629</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G196" s="2">
         <v>19.65</v>
@@ -7375,27 +7058,29 @@
         <v>0</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="197" spans="1:10">
       <c r="A197" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B197" s="2">
-        <v>46027.70638888889</v>
+        <v>46027.33265046297</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D197" s="2"/>
-      <c r="E197" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D197" s="2">
+        <v>46027.59347222222</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="F197" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G197" s="2">
-        <v>19.65</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G197" s="2"/>
       <c r="H197" s="2">
         <v>0</v>
       </c>
@@ -7403,31 +7088,29 @@
         <v>0</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="198" spans="1:10">
       <c r="A198" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B198" s="2">
-        <v>46027.32223379629</v>
+        <v>46027.5818287037</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D198" s="2">
-        <v>46027.68295138889</v>
+        <v>46027.68847222222</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G198" s="2">
-        <v>26.5</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G198" s="2"/>
       <c r="H198" s="2">
         <v>0</v>
       </c>
@@ -7435,31 +7118,29 @@
         <v>0</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="199" spans="1:10">
       <c r="A199" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B199" s="2">
-        <v>46027.39368055556</v>
+        <v>46027.61831018519</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D199" s="2">
-        <v>46027.67783564814</v>
+        <v>46027.68756944445</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G199" s="2">
-        <v>26.8</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G199" s="2"/>
       <c r="H199" s="2">
         <v>0</v>
       </c>
@@ -7467,31 +7148,29 @@
         <v>0</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="200" spans="1:10">
       <c r="A200" s="2" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="B200" s="2">
-        <v>46027.70658564815</v>
+        <v>46027.53438657407</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D200" s="2">
-        <v>46027.72515046296</v>
+        <v>46027.68799768519</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G200" s="2">
-        <v>26.8</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G200" s="2"/>
       <c r="H200" s="2">
         <v>0</v>
       </c>
@@ -7499,31 +7178,29 @@
         <v>0</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="201" spans="1:10">
       <c r="A201" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B201" s="2">
-        <v>46027.25033564815</v>
+        <v>46027.70658564815</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D201" s="2">
-        <v>46027.67822916667</v>
+        <v>46027.72515046296</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G201" s="2">
-        <v>31.26</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="G201" s="2"/>
       <c r="H201" s="2">
         <v>0</v>
       </c>
@@ -7531,31 +7208,29 @@
         <v>0</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="202" spans="1:10">
       <c r="A202" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B202" s="2">
-        <v>46027.22513888889</v>
+        <v>46027.32223379629</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D202" s="2">
-        <v>46027.68486111111</v>
+        <v>46027.68295138889</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G202" s="2">
-        <v>30.78</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="G202" s="2"/>
       <c r="H202" s="2">
         <v>0</v>
       </c>
@@ -7563,31 +7238,29 @@
         <v>0</v>
       </c>
       <c r="J202" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="203" spans="1:10">
       <c r="A203" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B203" s="2">
-        <v>46027.29422453704</v>
+        <v>46027.39368055556</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D203" s="2">
-        <v>46027.598125</v>
+        <v>46027.67783564814</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G203" s="2">
-        <v>33.81</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="G203" s="2"/>
       <c r="H203" s="2">
         <v>0</v>
       </c>
@@ -7595,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="J203" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -7603,23 +7276,21 @@
         <v>177</v>
       </c>
       <c r="B204" s="2">
-        <v>46027.35130787037</v>
+        <v>46027.25033564815</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D204" s="2">
-        <v>46027.57915509259</v>
+        <v>46027.67822916667</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G204" s="2">
-        <v>30.78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="G204" s="2"/>
       <c r="H204" s="2">
         <v>0</v>
       </c>
@@ -7627,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="J204" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -7635,23 +7306,21 @@
         <v>178</v>
       </c>
       <c r="B205" s="2">
-        <v>46027.33660879629</v>
+        <v>46027.29422453704</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D205" s="2">
-        <v>46027.73024305556</v>
+        <v>46027.598125</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G205" s="2">
-        <v>32.59</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="G205" s="2"/>
       <c r="H205" s="2">
         <v>0</v>
       </c>
@@ -7659,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="J205" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -7670,20 +7339,18 @@
         <v>46027.35273148148</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D206" s="2">
         <v>46027.72333333334</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G206" s="2">
-        <v>30.78</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="G206" s="2"/>
       <c r="H206" s="2">
         <v>0</v>
       </c>
@@ -7691,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="J206" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -7699,23 +7366,21 @@
         <v>180</v>
       </c>
       <c r="B207" s="2">
-        <v>46027.35745370371</v>
+        <v>46027.33660879629</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D207" s="2">
-        <v>46027.73527777778</v>
+        <v>46027.73024305556</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="G207" s="2">
-        <v>23</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="G207" s="2"/>
       <c r="H207" s="2">
         <v>0</v>
       </c>
@@ -7723,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="J207" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -7731,23 +7396,21 @@
         <v>181</v>
       </c>
       <c r="B208" s="2">
-        <v>46027.32341435185</v>
+        <v>46027.22513888889</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D208" s="2">
-        <v>46027.71140046296</v>
+        <v>46027.68486111111</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G208" s="2">
-        <v>23</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="G208" s="2"/>
       <c r="H208" s="2">
         <v>0</v>
       </c>
@@ -7755,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="J208" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -7763,19 +7426,21 @@
         <v>182</v>
       </c>
       <c r="B209" s="2">
-        <v>46027.33532407408</v>
+        <v>46027.35130787037</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D209" s="2"/>
-      <c r="E209" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="D209" s="2">
+        <v>46027.57915509259</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F209" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G209" s="2">
-        <v>26.75</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="G209" s="2"/>
       <c r="H209" s="2">
         <v>0</v>
       </c>
@@ -7783,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="J209" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -7791,23 +7456,21 @@
         <v>183</v>
       </c>
       <c r="B210" s="2">
-        <v>46027.33181712963</v>
+        <v>46027.35745370371</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D210" s="2">
-        <v>46027.666875</v>
+        <v>46027.73527777778</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G210" s="2">
-        <v>20.2</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="G210" s="2"/>
       <c r="H210" s="2">
         <v>0</v>
       </c>
@@ -7815,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="2" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -7823,31 +7486,119 @@
         <v>184</v>
       </c>
       <c r="B211" s="2">
+        <v>46027.33532407408</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D211" s="2">
+        <v>46027.6875</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2">
+        <v>0</v>
+      </c>
+      <c r="I211" s="2">
+        <v>0</v>
+      </c>
+      <c r="J211" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="A212" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B212" s="2">
+        <v>46027.32341435185</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D212" s="2">
+        <v>46027.71140046296</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2">
+        <v>0</v>
+      </c>
+      <c r="I212" s="2">
+        <v>0</v>
+      </c>
+      <c r="J212" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="A213" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B213" s="2">
         <v>46027.32818287037</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="C213" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D213" s="2">
+        <v>46027.66224537037</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2">
+        <v>0</v>
+      </c>
+      <c r="I213" s="2">
+        <v>0</v>
+      </c>
+      <c r="J213" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="A214" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D211" s="2">
-        <v>46027.66224537037</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G211" s="2">
-        <v>28.4</v>
-      </c>
-      <c r="H211" s="2">
-        <v>0</v>
-      </c>
-      <c r="I211" s="2">
-        <v>0</v>
-      </c>
-      <c r="J211" s="2" t="s">
-        <v>188</v>
+      <c r="B214" s="2">
+        <v>46027.33181712963</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D214" s="2">
+        <v>46027.666875</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2">
+        <v>0</v>
+      </c>
+      <c r="I214" s="2">
+        <v>0</v>
+      </c>
+      <c r="J214" s="2" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
